--- a/кейс2_каналы_продаж/Кейс2_Каналы_продаж_ФУТБОЛКИ.xlsx
+++ b/кейс2_каналы_продаж/Кейс2_Каналы_продаж_ФУТБОЛКИ.xlsx
@@ -1678,112 +1678,34 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6">
-        <f>Анализ!A10</f>
-        <v/>
-      </c>
-      <c r="B11" s="7">
-        <f>Анализ!B10</f>
-        <v/>
-      </c>
-      <c r="C11" s="45">
-        <f>Анализ!M10</f>
-        <v/>
-      </c>
-      <c r="D11" s="46">
-        <f>Анализ!P10</f>
-        <v/>
-      </c>
-      <c r="E11" s="10">
-        <f>IF(Анализ!$M$12=0,1,(C11/Анализ!$M$12)^Данные!$B$18)</f>
-        <v/>
-      </c>
-      <c r="F11" s="10">
-        <f>MIN(MAX(E11,Данные!$B$20),Данные!$B$19)</f>
-        <v/>
-      </c>
-      <c r="G11" s="7">
-        <f>B11*F11</f>
-        <v/>
-      </c>
-      <c r="H11" s="46">
-        <f>IF($G$13=0,0,G11/$G$13)</f>
-        <v/>
-      </c>
-      <c r="I11" s="11">
-        <f>ROUND(H11*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="47">
-        <f>I11-B11</f>
-        <v/>
-      </c>
-      <c r="K11" s="48">
-        <f>IF(B11=0,0,I11/B11-1)</f>
-        <v/>
-      </c>
-      <c r="L11" s="14">
-        <f>IF(K11&gt;Данные!$B$21,"Увеличить",IF(K11&lt;-Данные!$B$21,"Сократить","Сохранить"))</f>
-        <v/>
-      </c>
-      <c r="M11" s="7">
-        <f>I11*C11</f>
-        <v/>
-      </c>
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="46" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="46" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="47" t="n"/>
+      <c r="K11" s="48" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6">
-        <f>Анализ!A11</f>
-        <v/>
-      </c>
-      <c r="B12" s="7">
-        <f>Анализ!B11</f>
-        <v/>
-      </c>
-      <c r="C12" s="45">
-        <f>Анализ!M11</f>
-        <v/>
-      </c>
-      <c r="D12" s="46">
-        <f>Анализ!P11</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>IF(Анализ!$M$12=0,1,(C12/Анализ!$M$12)^Данные!$B$18)</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>MIN(MAX(E12,Данные!$B$20),Данные!$B$19)</f>
-        <v/>
-      </c>
-      <c r="G12" s="7">
-        <f>B12*F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="46">
-        <f>IF($G$13=0,0,G12/$G$13)</f>
-        <v/>
-      </c>
-      <c r="I12" s="11">
-        <f>ROUND(H12*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="47">
-        <f>I12-B12</f>
-        <v/>
-      </c>
-      <c r="K12" s="48">
-        <f>IF(B12=0,0,I12/B12-1)</f>
-        <v/>
-      </c>
-      <c r="L12" s="14">
-        <f>IF(K12&gt;Данные!$B$21,"Увеличить",IF(K12&lt;-Данные!$B$21,"Сократить","Сохранить"))</f>
-        <v/>
-      </c>
-      <c r="M12" s="7">
-        <f>I12*C12</f>
-        <v/>
-      </c>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="46" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="46" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="47" t="n"/>
+      <c r="K12" s="48" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -2151,114 +2073,76 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Блогеры (интеграции)</t>
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>312000</v>
+        <v>420000</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>1740000</v>
+        <v>1020000</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>69600</v>
+        <v>20400</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>6264</v>
+        <v>1632</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>648</v>
+        <v>240</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2196720</v>
+        <v>732240</v>
       </c>
       <c r="H8" s="55" t="n">
-        <v>0.49</v>
+        <v>0.6028</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Канал n — таргет VK</t>
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>360000</v>
+        <v>264000</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>2016000</v>
+        <v>1152000</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>70560</v>
+        <v>9216</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>5640</v>
+        <v>372</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>540</v>
+        <v>36</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>1830600</v>
+        <v>122040</v>
       </c>
       <c r="H9" s="55" t="n">
-        <v>0.4746</v>
+        <v>0.6404</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Блогеры (интеграции)</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="n">
-        <v>420000</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>1020000</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>20400</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>1632</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>240</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>732240</v>
-      </c>
-      <c r="H10" s="55" t="n">
-        <v>0.6028</v>
-      </c>
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Канал n — таргет VK</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="n">
-        <v>264000</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>1152000</v>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>9216</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>372</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>122040</v>
-      </c>
-      <c r="H11" s="55" t="n">
-        <v>0.6404</v>
-      </c>
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -3011,168 +2895,48 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6">
-        <f>Данные!A10</f>
-        <v/>
-      </c>
-      <c r="B10" s="7">
-        <f>Данные!B10</f>
-        <v/>
-      </c>
-      <c r="C10" s="7">
-        <f>Данные!G10</f>
-        <v/>
-      </c>
-      <c r="D10" s="36">
-        <f>Данные!F10</f>
-        <v/>
-      </c>
-      <c r="E10" s="7">
-        <f>IF(D10=0,0,C10/D10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="46">
-        <f>IF(Данные!C10=0,0,Данные!D10/Данные!C10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="46">
-        <f>IF(Данные!D10=0,0,Данные!E10/Данные!D10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="46">
-        <f>IF(Данные!E10=0,0,Данные!F10/Данные!E10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="37">
-        <f>IF(Данные!C10=0,0,Данные!F10/Данные!C10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="7">
-        <f>IF(Данные!D10=0,0,B10/Данные!D10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="7">
-        <f>IF(Данные!E10=0,0,B10/Данные!E10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="7">
-        <f>IF(D10=0,0,B10/D10)</f>
-        <v/>
-      </c>
-      <c r="M10" s="45">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="46">
-        <f>IF(C10=0,0,B10/C10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="7">
-        <f>C10*Данные!$H10</f>
-        <v/>
-      </c>
-      <c r="P10" s="46">
-        <f>IF(B10=0,0,(O10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="46">
-        <f>IF($B$12=0,0,B10/$B$12)</f>
-        <v/>
-      </c>
-      <c r="R10" s="46">
-        <f>IF($C$12=0,0,C10/$C$12)</f>
-        <v/>
-      </c>
-      <c r="S10" s="38">
-        <f>RANK(M10,$M$5:$M$11)</f>
-        <v/>
-      </c>
-      <c r="T10" s="6">
-        <f>IF(Данные!$H10=0,"",IF(M10&lt;1/Данные!$H10,"Убыточен — сократить",IF(M10&gt;=$M$12,"Лидер — наращивать","Ниже среднего — оптимизировать")))</f>
-        <v/>
-      </c>
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="46" t="n"/>
+      <c r="G10" s="46" t="n"/>
+      <c r="H10" s="46" t="n"/>
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="45" t="n"/>
+      <c r="N10" s="46" t="n"/>
+      <c r="O10" s="7" t="n"/>
+      <c r="P10" s="46" t="n"/>
+      <c r="Q10" s="46" t="n"/>
+      <c r="R10" s="46" t="n"/>
+      <c r="S10" s="38" t="n"/>
+      <c r="T10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6">
-        <f>Данные!A11</f>
-        <v/>
-      </c>
-      <c r="B11" s="7">
-        <f>Данные!B11</f>
-        <v/>
-      </c>
-      <c r="C11" s="7">
-        <f>Данные!G11</f>
-        <v/>
-      </c>
-      <c r="D11" s="36">
-        <f>Данные!F11</f>
-        <v/>
-      </c>
-      <c r="E11" s="7">
-        <f>IF(D11=0,0,C11/D11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="46">
-        <f>IF(Данные!C11=0,0,Данные!D11/Данные!C11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="46">
-        <f>IF(Данные!D11=0,0,Данные!E11/Данные!D11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="46">
-        <f>IF(Данные!E11=0,0,Данные!F11/Данные!E11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="37">
-        <f>IF(Данные!C11=0,0,Данные!F11/Данные!C11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="7">
-        <f>IF(Данные!D11=0,0,B11/Данные!D11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="7">
-        <f>IF(Данные!E11=0,0,B11/Данные!E11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="7">
-        <f>IF(D11=0,0,B11/D11)</f>
-        <v/>
-      </c>
-      <c r="M11" s="45">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="46">
-        <f>IF(C11=0,0,B11/C11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="7">
-        <f>C11*Данные!$H11</f>
-        <v/>
-      </c>
-      <c r="P11" s="46">
-        <f>IF(B11=0,0,(O11-B11)/B11)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="46">
-        <f>IF($B$12=0,0,B11/$B$12)</f>
-        <v/>
-      </c>
-      <c r="R11" s="46">
-        <f>IF($C$12=0,0,C11/$C$12)</f>
-        <v/>
-      </c>
-      <c r="S11" s="38">
-        <f>RANK(M11,$M$5:$M$11)</f>
-        <v/>
-      </c>
-      <c r="T11" s="6">
-        <f>IF(Данные!$H11=0,"",IF(M11&lt;1/Данные!$H11,"Убыточен — сократить",IF(M11&gt;=$M$12,"Лидер — наращивать","Ниже среднего — оптимизировать")))</f>
-        <v/>
-      </c>
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="46" t="n"/>
+      <c r="G11" s="46" t="n"/>
+      <c r="H11" s="46" t="n"/>
+      <c r="I11" s="37" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="45" t="n"/>
+      <c r="N11" s="46" t="n"/>
+      <c r="O11" s="7" t="n"/>
+      <c r="P11" s="46" t="n"/>
+      <c r="Q11" s="46" t="n"/>
+      <c r="R11" s="46" t="n"/>
+      <c r="S11" s="38" t="n"/>
+      <c r="T11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -3780,88 +3544,28 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6">
-        <f>Данные!A10</f>
-        <v/>
-      </c>
-      <c r="B19" s="36">
-        <f>Данные!C10</f>
-        <v/>
-      </c>
-      <c r="C19" s="36">
-        <f>Данные!D10</f>
-        <v/>
-      </c>
-      <c r="D19" s="36">
-        <f>Данные!E10</f>
-        <v/>
-      </c>
-      <c r="E19" s="36">
-        <f>Данные!F10</f>
-        <v/>
-      </c>
-      <c r="F19" s="46">
-        <f>IF(B19=0,0,C19/B19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="46">
-        <f>IF(C19=0,0,D19/C19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="46">
-        <f>IF(D19=0,0,E19/D19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="37">
-        <f>IF(B19=0,0,E19/B19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="6">
-        <f>IF(F19/F$21&lt;=MIN(G19/G$21,H19/H$21),"клик: показ → переход",IF(G19/G$21&lt;=H19/H$21,"корзина: переход → интерес","оплата: интерес → заказ"))</f>
-        <v/>
-      </c>
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="46" t="n"/>
+      <c r="G19" s="46" t="n"/>
+      <c r="H19" s="46" t="n"/>
+      <c r="I19" s="37" t="n"/>
+      <c r="J19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6">
-        <f>Данные!A11</f>
-        <v/>
-      </c>
-      <c r="B20" s="36">
-        <f>Данные!C11</f>
-        <v/>
-      </c>
-      <c r="C20" s="36">
-        <f>Данные!D11</f>
-        <v/>
-      </c>
-      <c r="D20" s="36">
-        <f>Данные!E11</f>
-        <v/>
-      </c>
-      <c r="E20" s="36">
-        <f>Данные!F11</f>
-        <v/>
-      </c>
-      <c r="F20" s="46">
-        <f>IF(B20=0,0,C20/B20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="46">
-        <f>IF(C20=0,0,D20/C20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="46">
-        <f>IF(D20=0,0,E20/D20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="37">
-        <f>IF(B20=0,0,E20/B20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="6">
-        <f>IF(F20/F$21&lt;=MIN(G20/G$21,H20/H$21),"клик: показ → переход",IF(G20/G$21&lt;=H20/H$21,"корзина: переход → интерес","оплата: интерес → заказ"))</f>
-        <v/>
-      </c>
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="46" t="n"/>
+      <c r="G20" s="46" t="n"/>
+      <c r="H20" s="46" t="n"/>
+      <c r="I20" s="37" t="n"/>
+      <c r="J20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">

--- a/кейс2_каналы_продаж/Кейс2_Каналы_продаж_ФУТБОЛКИ.xlsx
+++ b/кейс2_каналы_продаж/Кейс2_Каналы_продаж_ФУТБОЛКИ.xlsx
@@ -1935,7 +1935,7 @@
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>Факт за 12 месяцев. Юнит-экономика согласована с Кейсом 1: цена 3 390 ₽, себестоимость 851 ₽ (футболка 780 + принт 46 + упаковка 25), у блогеров промокод −10%.</t>
+          <t>Факт за 12 месяцев (месячный срез таблицы × 12). Юнит-экономика согласована с Кейсом 1: цена 3 390 ₽, себестоимость 851 ₽ (футболка 780 + принт 46 + упаковка 25), у блогеров промокод −10%.</t>
         </is>
       </c>
     </row>
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>204000</v>
+        <v>60000</v>
       </c>
       <c r="C5" s="29" t="n">
-        <v>336000</v>
+        <v>312000</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>25200</v>
+        <v>3120</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>2520</v>
+        <v>624</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>1627200</v>
+        <v>528840</v>
       </c>
       <c r="H5" s="55" t="n">
         <v>0.6404</v>
@@ -2021,16 +2021,16 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>288000</v>
+        <v>144000</v>
       </c>
       <c r="C6" s="29" t="n">
-        <v>1560000</v>
+        <v>1440000</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>13200</v>
+        <v>14400</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>924</v>
+        <v>1152</v>
       </c>
       <c r="F6" s="29" t="n">
         <v>144</v>
@@ -2049,22 +2049,22 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>216000</v>
+        <v>144000</v>
       </c>
       <c r="C7" s="29" t="n">
-        <v>744000</v>
+        <v>72000</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>29760</v>
+        <v>21600</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>2676</v>
+        <v>2160</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>1139040</v>
+        <v>1220400</v>
       </c>
       <c r="H7" s="55" t="n">
         <v>0.3546</v>
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>420000</v>
+        <v>180000</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>1020000</v>
+        <v>960000</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>20400</v>
+        <v>19200</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>1632</v>
+        <v>1920</v>
       </c>
       <c r="F8" s="29" t="n">
         <v>240</v>
@@ -2101,29 +2101,29 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Канал n — таргет VK</t>
+          <t>ВК Канал (Таргет ВК)</t>
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>264000</v>
+        <v>120000</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>1152000</v>
+        <v>1200000</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>9216</v>
+        <v>8400</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>372</v>
+        <v>240</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>122040</v>
+        <v>284760</v>
       </c>
       <c r="H9" s="55" t="n">
-        <v>0.6404</v>
+        <v>0.5201</v>
       </c>
     </row>
     <row r="10">

--- a/кейс2_каналы_продаж/Кейс2_Каналы_продаж_ФУТБОЛКИ.xlsx
+++ b/кейс2_каналы_продаж/Кейс2_Каналы_продаж_ФУТБОЛКИ.xlsx
@@ -2052,7 +2052,7 @@
         <v>144000</v>
       </c>
       <c r="C7" s="29" t="n">
-        <v>72000</v>
+        <v>720000</v>
       </c>
       <c r="D7" s="29" t="n">
         <v>21600</v>
